--- a/research/traditional_assets/database/data/finland/finland_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_drugs_biotechnology.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-27.01</v>
+        <v>-28.08</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10.55</v>
+        <v>13.94</v>
       </c>
       <c r="V2">
-        <v>0.05021418372203712</v>
+        <v>0.06106000876040299</v>
       </c>
       <c r="W2">
-        <v>-1.638679530135262</v>
+        <v>-4.001816472874357</v>
       </c>
       <c r="X2">
-        <v>0.07181311421698622</v>
+        <v>0.141998831190587</v>
       </c>
       <c r="Y2">
-        <v>-1.710492644352248</v>
+        <v>-4.143815304064944</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
-      <c r="AA2">
-        <v>6.834182199549928</v>
-      </c>
       <c r="AB2">
-        <v>0.06388798054614334</v>
-      </c>
-      <c r="AC2">
-        <v>6.770294219003786</v>
+        <v>0.1201213165994524</v>
       </c>
       <c r="AD2">
-        <v>11.26</v>
+        <v>19.6</v>
       </c>
       <c r="AE2">
-        <v>0.06390810254797055</v>
+        <v>0.04503098290913679</v>
       </c>
       <c r="AF2">
-        <v>11.32390810254797</v>
+        <v>19.64503098290914</v>
       </c>
       <c r="AG2">
-        <v>0.7739081025479706</v>
+        <v>5.705030982909136</v>
       </c>
       <c r="AH2">
-        <v>0.05114130718577839</v>
+        <v>0.07923139618903381</v>
       </c>
       <c r="AI2">
-        <v>0.556897771222297</v>
+        <v>0.9854527439536651</v>
       </c>
       <c r="AJ2">
-        <v>0.00367000407737319</v>
+        <v>0.02437995011878959</v>
       </c>
       <c r="AK2">
-        <v>0.07910009930964354</v>
+        <v>0.9516266052958287</v>
       </c>
       <c r="AL2">
-        <v>0.228</v>
+        <v>0.866</v>
       </c>
       <c r="AM2">
-        <v>0.182</v>
+        <v>0.204</v>
       </c>
       <c r="AN2">
-        <v>-0.4296561987255313</v>
+        <v>-0.6192733017377567</v>
       </c>
       <c r="AO2">
-        <v>-116.7105263157895</v>
+        <v>-36.96304849884527</v>
       </c>
       <c r="AP2">
-        <v>-0.02953058734490673</v>
+        <v>-0.1802537435358337</v>
       </c>
       <c r="AQ2">
-        <v>-146.2087912087912</v>
+        <v>-156.9117647058824</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +683,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Faron Pharmaceuticals Oy (AIM:FARN)</t>
+          <t>BBS-Bioactive Bone Substitutes Oyj (HLSE:BONEH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -698,7 +692,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-23.9</v>
+        <v>-3.28</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +716,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>8.26</v>
+        <v>3.54</v>
       </c>
       <c r="V3">
-        <v>0.04284232365145228</v>
+        <v>0.2925619834710744</v>
       </c>
       <c r="W3">
-        <v>-2.904009720534629</v>
+        <v>-0.5784832451499118</v>
       </c>
       <c r="X3">
-        <v>0.06431014125873424</v>
+        <v>0.1583670838745743</v>
       </c>
       <c r="Y3">
-        <v>-2.968319861793363</v>
+        <v>-0.7368503290244861</v>
       </c>
       <c r="Z3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>13.9848733370599</v>
+        <v>-0.2779369627507164</v>
       </c>
       <c r="AB3">
-        <v>0.06351938301030956</v>
+        <v>0.1190026151289166</v>
       </c>
       <c r="AC3">
-        <v>13.92135395404959</v>
+        <v>-0.396939577879633</v>
       </c>
       <c r="AD3">
-        <v>4.17</v>
+        <v>6.7</v>
       </c>
       <c r="AE3">
-        <v>0.06390810254797055</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.233908102547971</v>
+        <v>6.7</v>
       </c>
       <c r="AG3">
-        <v>-4.026091897452029</v>
+        <v>3.16</v>
       </c>
       <c r="AH3">
-        <v>0.02148822069927374</v>
+        <v>0.3563829787234042</v>
       </c>
       <c r="AI3">
-        <v>0.5590123414784534</v>
+        <v>0.5394524959742352</v>
       </c>
       <c r="AJ3">
-        <v>-0.02132758673017951</v>
+        <v>0.2070773263433814</v>
       </c>
       <c r="AK3">
-        <v>5.868152520681136</v>
+        <v>0.3558558558558559</v>
       </c>
       <c r="AL3">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="AM3">
-        <v>0.08400000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="AN3">
-        <v>-0.1776963395406315</v>
+        <v>-2.50936329588015</v>
       </c>
       <c r="AO3">
-        <v>-181.5384615384615</v>
+        <v>-7.864864864864865</v>
       </c>
       <c r="AP3">
-        <v>0.1715639790962641</v>
+        <v>-1.183520599250936</v>
       </c>
       <c r="AQ3">
-        <v>-280.952380952381</v>
+        <v>-7.864864864864865</v>
       </c>
     </row>
     <row r="4">
@@ -799,7 +793,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BBS-Bioactive Bone Substitutes Oyj (HLSE:BONEH)</t>
+          <t>Faron Pharmaceuticals Oy (AIM:FARN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -808,7 +802,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-3.11</v>
+        <v>-24.8</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -832,73 +826,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.29</v>
+        <v>10.4</v>
       </c>
       <c r="V4">
-        <v>0.1323699421965318</v>
+        <v>0.0481036077705828</v>
       </c>
       <c r="W4">
-        <v>-0.3733493397358943</v>
+        <v>-7.425149700598803</v>
       </c>
       <c r="X4">
-        <v>0.07931608717523821</v>
+        <v>0.1256305785065997</v>
       </c>
       <c r="Y4">
-        <v>-0.4526654269111325</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>-0.316508937960042</v>
+        <v>-7.550780279105403</v>
       </c>
       <c r="AB4">
-        <v>0.0642565780819771</v>
-      </c>
-      <c r="AC4">
-        <v>-0.3807655160420191</v>
+        <v>0.1212400180699881</v>
       </c>
       <c r="AD4">
-        <v>7.09</v>
+        <v>12.9</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.04503098290913679</v>
       </c>
       <c r="AF4">
-        <v>7.09</v>
+        <v>12.94503098290914</v>
       </c>
       <c r="AG4">
-        <v>4.8</v>
+        <v>2.545030982909136</v>
       </c>
       <c r="AH4">
-        <v>0.2906929069290693</v>
+        <v>0.05649274141962365</v>
       </c>
       <c r="AI4">
-        <v>0.5556426332288401</v>
+        <v>1.722551911276086</v>
       </c>
       <c r="AJ4">
-        <v>0.2171945701357466</v>
+        <v>0.01163469163835764</v>
       </c>
       <c r="AK4">
-        <v>0.4584527220630373</v>
+        <v>-0.8821692599927768</v>
       </c>
       <c r="AL4">
-        <v>0.098</v>
+        <v>0.496</v>
       </c>
       <c r="AM4">
-        <v>0.098</v>
+        <v>-0.166</v>
       </c>
       <c r="AN4">
-        <v>-2.587591240875912</v>
+        <v>-0.4451345755693582</v>
       </c>
       <c r="AO4">
-        <v>-30.71428571428571</v>
+        <v>-58.66935483870968</v>
       </c>
       <c r="AP4">
-        <v>-1.751824817518248</v>
+        <v>-0.08782025475876935</v>
       </c>
       <c r="AQ4">
-        <v>-30.71428571428571</v>
+        <v>175.3012048192771</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_drugs_biotechnology.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-28.08</v>
+        <v>-35.34</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,67 +612,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>13.94</v>
+        <v>8.709999999999999</v>
       </c>
       <c r="V2">
-        <v>0.06106000876040299</v>
+        <v>0.03137608069164265</v>
       </c>
       <c r="W2">
-        <v>-4.001816472874357</v>
+        <v>2.654634959883579</v>
       </c>
       <c r="X2">
-        <v>0.141998831190587</v>
+        <v>0.1156148742417174</v>
       </c>
       <c r="Y2">
-        <v>-4.143815304064944</v>
+        <v>2.539020085641861</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1201213165994524</v>
+        <v>0.09731789466215265</v>
       </c>
       <c r="AD2">
-        <v>19.6</v>
+        <v>21.65</v>
       </c>
       <c r="AE2">
-        <v>0.04503098290913679</v>
+        <v>0.07107599934768222</v>
       </c>
       <c r="AF2">
-        <v>19.64503098290914</v>
+        <v>21.72107599934768</v>
       </c>
       <c r="AG2">
-        <v>5.705030982909136</v>
+        <v>13.01107599934768</v>
       </c>
       <c r="AH2">
-        <v>0.07923139618903381</v>
+        <v>0.07256781343187146</v>
       </c>
       <c r="AI2">
-        <v>0.9854527439536651</v>
+        <v>1.350722799906473</v>
       </c>
       <c r="AJ2">
-        <v>0.02437995011878959</v>
+        <v>0.04477143878499969</v>
       </c>
       <c r="AK2">
-        <v>0.9516266052958287</v>
+        <v>1.765152875984337</v>
       </c>
       <c r="AL2">
-        <v>0.866</v>
+        <v>2.864</v>
       </c>
       <c r="AM2">
-        <v>0.204</v>
+        <v>2.864</v>
       </c>
       <c r="AN2">
-        <v>-0.6192733017377567</v>
+        <v>-0.6735106548452324</v>
       </c>
       <c r="AO2">
-        <v>-36.96304849884527</v>
+        <v>-11.36871508379888</v>
       </c>
       <c r="AP2">
-        <v>-0.1802537435358337</v>
+        <v>-0.4047620469543531</v>
       </c>
       <c r="AQ2">
-        <v>-156.9117647058824</v>
+        <v>-11.36871508379888</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-3.28</v>
+        <v>-3.34</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,73 +716,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.54</v>
+        <v>1.82</v>
       </c>
       <c r="V3">
-        <v>0.2925619834710744</v>
+        <v>0.175</v>
       </c>
       <c r="W3">
-        <v>-0.5784832451499118</v>
+        <v>-0.583916083916084</v>
       </c>
       <c r="X3">
-        <v>0.1583670838745743</v>
+        <v>0.1302219419003602</v>
       </c>
       <c r="Y3">
-        <v>-0.7368503290244861</v>
+        <v>-0.7141380258164443</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.2779369627507164</v>
+        <v>-0.3671171171171171</v>
       </c>
       <c r="AB3">
-        <v>0.1190026151289166</v>
+        <v>0.09660560234980513</v>
       </c>
       <c r="AC3">
-        <v>-0.396939577879633</v>
+        <v>-0.4637227194669223</v>
       </c>
       <c r="AD3">
-        <v>6.7</v>
+        <v>6.95</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.7</v>
+        <v>6.95</v>
       </c>
       <c r="AG3">
-        <v>3.16</v>
+        <v>5.13</v>
       </c>
       <c r="AH3">
-        <v>0.3563829787234042</v>
+        <v>0.4005763688760807</v>
       </c>
       <c r="AI3">
-        <v>0.5394524959742352</v>
+        <v>0.5935098206660974</v>
       </c>
       <c r="AJ3">
-        <v>0.2070773263433814</v>
+        <v>0.3303283966516419</v>
       </c>
       <c r="AK3">
-        <v>0.3558558558558559</v>
+        <v>0.5187057633973711</v>
       </c>
       <c r="AL3">
-        <v>0.37</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AM3">
-        <v>0.37</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AN3">
-        <v>-2.50936329588015</v>
+        <v>-2.301324503311258</v>
       </c>
       <c r="AO3">
-        <v>-7.864864864864865</v>
+        <v>-38.8095238095238</v>
       </c>
       <c r="AP3">
-        <v>-1.183520599250936</v>
+        <v>-1.698675496688742</v>
       </c>
       <c r="AQ3">
-        <v>-7.864864864864865</v>
+        <v>-38.8095238095238</v>
       </c>
     </row>
     <row r="4">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-24.8</v>
+        <v>-32</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -826,64 +826,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>10.4</v>
+        <v>6.89</v>
       </c>
       <c r="V4">
-        <v>0.0481036077705828</v>
+        <v>0.02578592814371258</v>
       </c>
       <c r="W4">
-        <v>-7.425149700598803</v>
+        <v>5.893186003683241</v>
       </c>
       <c r="X4">
-        <v>0.1256305785065997</v>
+        <v>0.1010078065830745</v>
       </c>
       <c r="Y4">
-        <v>-7.550780279105403</v>
+        <v>5.792178197100167</v>
       </c>
       <c r="AB4">
-        <v>0.1212400180699881</v>
+        <v>0.09803018697450019</v>
       </c>
       <c r="AD4">
-        <v>12.9</v>
+        <v>14.7</v>
       </c>
       <c r="AE4">
-        <v>0.04503098290913679</v>
+        <v>0.07107599934768222</v>
       </c>
       <c r="AF4">
-        <v>12.94503098290914</v>
+        <v>14.77107599934768</v>
       </c>
       <c r="AG4">
-        <v>2.545030982909136</v>
+        <v>7.881075999347682</v>
       </c>
       <c r="AH4">
-        <v>0.05649274141962365</v>
+        <v>0.05238507512515878</v>
       </c>
       <c r="AI4">
-        <v>1.722551911276086</v>
+        <v>3.379276864907416</v>
       </c>
       <c r="AJ4">
-        <v>0.01163469163835764</v>
+        <v>0.02865001153102357</v>
       </c>
       <c r="AK4">
-        <v>-0.8821692599927768</v>
+        <v>-3.128747035363807</v>
       </c>
       <c r="AL4">
-        <v>0.496</v>
+        <v>2.78</v>
       </c>
       <c r="AM4">
-        <v>-0.166</v>
+        <v>2.78</v>
       </c>
       <c r="AN4">
-        <v>-0.4451345755693582</v>
+        <v>-0.5047210300429185</v>
       </c>
       <c r="AO4">
-        <v>-58.66935483870968</v>
+        <v>-10.53956834532374</v>
       </c>
       <c r="AP4">
-        <v>-0.08782025475876935</v>
+        <v>-0.2705948840977745</v>
       </c>
       <c r="AQ4">
-        <v>175.3012048192771</v>
+        <v>-10.53956834532374</v>
       </c>
     </row>
   </sheetData>
